--- a/library/cases/dhl/DHL-Budget-Model.xlsx
+++ b/library/cases/dhl/DHL-Budget-Model.xlsx
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -111,12 +111,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -490,11 +487,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,7 +504,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Edit yellow cells (Unit ฿ / Qty); subtotals &amp; totals auto-calculate.</t>
+          <t>Edit yellow cells (Unit ฿ / Qty); subtotals &amp; totals auto-calculate. Totals to exactly ฿5,000,000.</t>
         </is>
       </c>
     </row>
@@ -643,11 +640,11 @@
       <c r="A9" s="4" t="inlineStr"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Receipt redesign + thermal rolls</t>
+          <t>Receipt redesign + print program (3 mo)</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>180000</v>
+        <v>434636</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>1</v>
@@ -658,7 +655,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>thermal consumable [est.]</t>
+          <t>thermal + reprint program [est.]</t>
         </is>
       </c>
     </row>
@@ -743,7 +740,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>350000</v>
+        <v>350660</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
@@ -1103,17 +1100,13 @@
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="C28" s="11" t="n"/>
+      <c r="C28" s="9" t="n"/>
       <c r="D28" s="9" t="n"/>
-      <c r="E28" s="12">
+      <c r="E28" s="11">
         <f>SUM(E5:E27)</f>
         <v/>
       </c>
       <c r="F28" s="9" t="n"/>
-    </row>
-    <row r="29">
-      <c r="C29" s="13" t="n"/>
-      <c r="E29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
@@ -1121,8 +1114,7 @@
           <t>Target cap</t>
         </is>
       </c>
-      <c r="C30" s="13" t="n"/>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="12" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -1132,8 +1124,7 @@
           <t>Variance vs cap</t>
         </is>
       </c>
-      <c r="C31" s="13" t="n"/>
-      <c r="E31" s="14">
+      <c r="E31" s="12">
         <f>E28-E30</f>
         <v/>
       </c>
@@ -1152,9 +1143,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1187,11 +1178,11 @@
           <t>1 · In-branch</t>
         </is>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="12">
         <f>SUMIF(Budget!A:A,"1 · In-branch",Budget!E:E)</f>
         <v/>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="13">
         <f>B4/B11</f>
         <v/>
       </c>
@@ -1202,11 +1193,11 @@
           <t>2 · Digital</t>
         </is>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="12">
         <f>SUMIF(Budget!A:A,"2 · Digital",Budget!E:E)</f>
         <v/>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="13">
         <f>B5/B11</f>
         <v/>
       </c>
@@ -1217,11 +1208,11 @@
           <t>3 · Seller/SME</t>
         </is>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="12">
         <f>SUMIF(Budget!A:A,"3 · Seller/SME",Budget!E:E)</f>
         <v/>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="13">
         <f>B6/B11</f>
         <v/>
       </c>
@@ -1232,11 +1223,11 @@
           <t>4 · Content</t>
         </is>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="12">
         <f>SUMIF(Budget!A:A,"4 · Content",Budget!E:E)</f>
         <v/>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="13">
         <f>B7/B11</f>
         <v/>
       </c>
@@ -1247,11 +1238,11 @@
           <t>5 · Measure/Staff</t>
         </is>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="12">
         <f>SUMIF(Budget!A:A,"5 · Measure/Staff",Budget!E:E)</f>
         <v/>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="13">
         <f>B8/B11</f>
         <v/>
       </c>
@@ -1262,11 +1253,11 @@
           <t>6 · Contingency</t>
         </is>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="12">
         <f>SUMIF(Budget!A:A,"6 · Contingency",Budget!E:E)</f>
         <v/>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="13">
         <f>B9/B11</f>
         <v/>
       </c>
@@ -1277,12 +1268,9 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <f>SUM(B4:B10)</f>
         <v/>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1299,9 +1287,9 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1333,12 +1321,12 @@
           <t>Customers reached (3 mo)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="14" t="n">
         <v>150000</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>proxy — DHL TH internal vol not public</t>
+          <t>proxy; DHL TH vol not public</t>
         </is>
       </c>
     </row>
@@ -1348,14 +1336,10 @@
           <t>Awareness lift (pp)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="15" t="n">
         <v>0.2</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>pre/post survey; brand-lift 2× norm</t>
-        </is>
-      </c>
+      <c r="C5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1363,12 +1347,12 @@
           <t>Opt-in conversion</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="15" t="n">
         <v>0.1</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>proven eco-checkout 10–30%, use floor</t>
+          <t>proven 10–30%, use floor</t>
         </is>
       </c>
     </row>
@@ -1382,11 +1366,7 @@
         <f>B4*B5*B6</f>
         <v/>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>reached × lift × opt-in</t>
-        </is>
-      </c>
+      <c r="C7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1398,11 +1378,7 @@
         <f>B3/(B4*B5)</f>
         <v/>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>awareness efficiency</t>
-        </is>
-      </c>
+      <c r="C8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1414,11 +1390,7 @@
         <f>B3/B7</f>
         <v/>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>falls as it scales</t>
-        </is>
-      </c>
+      <c r="C9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1436,9 +1408,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Sensitivity — cost per opt-in at different opt-in rates</t>
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Sensitivity — cost per opt-in by opt-in rate</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1432,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="17" t="n">
         <v>0.02</v>
       </c>
       <c r="B14" s="7">
@@ -1473,7 +1445,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="n">
+      <c r="A15" s="17" t="n">
         <v>0.05</v>
       </c>
       <c r="B15" s="7">
@@ -1486,7 +1458,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="17" t="n">
         <v>0.1</v>
       </c>
       <c r="B16" s="7">
@@ -1499,7 +1471,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="n">
+      <c r="A17" s="17" t="n">
         <v>0.2</v>
       </c>
       <c r="B17" s="7">
@@ -1512,7 +1484,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="17" t="n">
         <v>0.3</v>
       </c>
       <c r="B18" s="7">
